--- a/02-Excel/Uncommon Excel Functions.xlsx
+++ b/02-Excel/Uncommon Excel Functions.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27628"/>
-  <workbookPr defaultThemeVersion="202300"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Videos\New Excel Vids\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\0-AI\DataAnalyst\DataAnalyst_Portfolio\02-Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="8_{F406FDA7-8609-4F72-B40E-786FD7F2373E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="14620" xr2:uid="{F40D0D0E-50EB-44A6-8777-284280D2A7CC}"/>
+    <workbookView xWindow="390" yWindow="390" windowWidth="21750" windowHeight="13890" xr2:uid="{F40D0D0E-50EB-44A6-8777-284280D2A7CC}"/>
   </bookViews>
   <sheets>
     <sheet name="PMT" sheetId="1" r:id="rId1"/>
@@ -40,14 +40,14 @@
 </file>
 
 <file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <metadataTypes count="1">
     <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
   </metadataTypes>
   <futureMetadata name="XLDAPR" count="1">
     <bk>
       <extLst>
-        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
+        <ext xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray" uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
           <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
         </ext>
       </extLst>
@@ -208,14 +208,14 @@
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Aptos Narrow"/>
+      <name val="Arial"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="0"/>
-      <name val="Aptos Narrow"/>
+      <name val="Arial"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -229,7 +229,7 @@
       <u/>
       <sz val="11"/>
       <color theme="10"/>
-      <name val="Aptos Narrow"/>
+      <name val="Arial"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -630,13 +630,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9CF720E4-ADF5-433A-B559-49440E23D4AA}">
   <dimension ref="A1:E6"/>
-  <sheetFormatPr defaultColWidth="14.1796875" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="14.125" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="3" max="3" width="17.26953125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="16.81640625" customWidth="1"/>
+    <col min="3" max="3" width="17.25" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="16.875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
@@ -653,7 +653,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A2">
         <v>1001</v>
       </c>
@@ -668,7 +668,7 @@
       </c>
       <c r="E2" s="5"/>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A3">
         <v>1002</v>
       </c>
@@ -683,7 +683,7 @@
       </c>
       <c r="E3" s="5"/>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A4">
         <v>1003</v>
       </c>
@@ -698,7 +698,7 @@
       </c>
       <c r="E4" s="5"/>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A5">
         <v>1004</v>
       </c>
@@ -713,7 +713,7 @@
       </c>
       <c r="E5" s="5"/>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A6">
         <v>1005</v>
       </c>
@@ -736,14 +736,14 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A7769E96-79C7-47CE-AAE6-D40319FE73CA}">
   <dimension ref="B5:P22"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="15" max="15" width="23.08984375" customWidth="1"/>
-    <col min="16" max="16" width="18.54296875" customWidth="1"/>
-    <col min="17" max="17" width="113.90625" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="23.125" customWidth="1"/>
+    <col min="16" max="16" width="18.5" customWidth="1"/>
+    <col min="17" max="17" width="113.875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="2:16" x14ac:dyDescent="0.35">
+    <row r="5" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C5" s="6" t="s">
         <v>5</v>
       </c>
@@ -787,7 +787,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="6" spans="2:16" x14ac:dyDescent="0.35">
+    <row r="6" spans="2:16" x14ac:dyDescent="0.2">
       <c r="B6" s="8" t="s">
         <v>18</v>
       </c>
@@ -836,7 +836,7 @@
         <v>774600</v>
       </c>
     </row>
-    <row r="7" spans="2:16" x14ac:dyDescent="0.35">
+    <row r="7" spans="2:16" x14ac:dyDescent="0.2">
       <c r="B7" s="8" t="s">
         <v>19</v>
       </c>
@@ -883,7 +883,7 @@
         <v>169405</v>
       </c>
     </row>
-    <row r="8" spans="2:16" x14ac:dyDescent="0.35">
+    <row r="8" spans="2:16" x14ac:dyDescent="0.2">
       <c r="B8" s="8" t="s">
         <v>20</v>
       </c>
@@ -930,7 +930,7 @@
         <v>116800</v>
       </c>
     </row>
-    <row r="9" spans="2:16" x14ac:dyDescent="0.35">
+    <row r="9" spans="2:16" x14ac:dyDescent="0.2">
       <c r="B9" s="8" t="s">
         <v>21</v>
       </c>
@@ -977,7 +977,7 @@
         <v>6604000</v>
       </c>
     </row>
-    <row r="10" spans="2:16" x14ac:dyDescent="0.35">
+    <row r="10" spans="2:16" x14ac:dyDescent="0.2">
       <c r="B10" s="8" t="s">
         <v>22</v>
       </c>
@@ -1024,7 +1024,7 @@
         <v>81000</v>
       </c>
     </row>
-    <row r="11" spans="2:16" x14ac:dyDescent="0.35">
+    <row r="11" spans="2:16" x14ac:dyDescent="0.2">
       <c r="B11" s="8" t="s">
         <v>23</v>
       </c>
@@ -1071,7 +1071,7 @@
         <v>2182800</v>
       </c>
     </row>
-    <row r="12" spans="2:16" x14ac:dyDescent="0.35">
+    <row r="12" spans="2:16" x14ac:dyDescent="0.2">
       <c r="B12" s="7" t="s">
         <v>24</v>
       </c>
@@ -1113,7 +1113,7 @@
         <v>1599</v>
       </c>
     </row>
-    <row r="16" spans="2:16" x14ac:dyDescent="0.35">
+    <row r="16" spans="2:16" x14ac:dyDescent="0.2">
       <c r="B16" s="4" t="s">
         <v>25</v>
       </c>
@@ -1121,7 +1121,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="17" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="17" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B17" t="s">
         <v>18</v>
       </c>
@@ -1134,7 +1134,7 @@
       </c>
       <c r="F17" s="9"/>
     </row>
-    <row r="18" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="18" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B18" t="s">
         <v>19</v>
       </c>
@@ -1147,7 +1147,7 @@
       </c>
       <c r="F18" s="9"/>
     </row>
-    <row r="19" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="19" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B19" t="s">
         <v>20</v>
       </c>
@@ -1159,7 +1159,7 @@
         <v>116800</v>
       </c>
     </row>
-    <row r="20" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="20" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B20" t="s">
         <v>21</v>
       </c>
@@ -1171,7 +1171,7 @@
         <v>6604000</v>
       </c>
     </row>
-    <row r="21" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="21" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B21" t="s">
         <v>22</v>
       </c>
@@ -1183,7 +1183,7 @@
         <v>81000</v>
       </c>
     </row>
-    <row r="22" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="22" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B22" t="s">
         <v>23</v>
       </c>
@@ -1203,9 +1203,9 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8524FEE7-F6CF-4A50-ABF4-A202B4363485}">
   <dimension ref="A1:D5"/>
-  <sheetFormatPr defaultColWidth="13.6328125" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="13.625" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A1" s="4" t="s">
         <v>27</v>
       </c>
@@ -1219,7 +1219,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>31</v>
       </c>
@@ -1230,7 +1230,7 @@
         <v>5000</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>33</v>
       </c>
@@ -1241,7 +1241,7 @@
         <v>7000</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>35</v>
       </c>
@@ -1252,7 +1252,7 @@
         <v>6000</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>37</v>
       </c>
@@ -1271,19 +1271,19 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EA8BBAA7-6627-4B97-ADF7-6694AF7A890A}">
   <dimension ref="A1:G4"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="27.90625" customWidth="1"/>
-    <col min="2" max="2" width="13.90625" customWidth="1"/>
+    <col min="1" max="1" width="27.875" customWidth="1"/>
+    <col min="2" max="2" width="13.875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A1" s="10" t="s">
         <v>42</v>
       </c>
       <c r="B1" s="10"/>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.2">
       <c r="G4" s="10"/>
     </row>
   </sheetData>
@@ -1297,14 +1297,14 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{45E6CD33-DF6B-4126-9765-9EC657996EDD}">
   <dimension ref="A1:C5"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="10.08984375" style="11" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="15.08984375" customWidth="1"/>
-    <col min="3" max="3" width="19.6328125" style="11" customWidth="1"/>
+    <col min="1" max="1" width="10.125" style="11" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="15.125" customWidth="1"/>
+    <col min="3" max="3" width="19.625" style="11" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1" s="13" t="s">
         <v>39</v>
       </c>
@@ -1315,7 +1315,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A2" s="11">
         <v>45292</v>
       </c>
@@ -1323,7 +1323,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A3" s="11">
         <v>45366</v>
       </c>
@@ -1331,7 +1331,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A4" s="11">
         <v>45463</v>
       </c>
@@ -1339,7 +1339,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A5" s="11">
         <v>45574</v>
       </c>
